--- a/docs/project-mto/Story Backlog - Batch 2 (Recognition & Progress Weight).xlsx
+++ b/docs/project-mto/Story Backlog - Batch 2 (Recognition & Progress Weight).xlsx
@@ -204,8 +204,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="AcceptanceCriteria" displayName="AcceptanceCriteria" ref="A1:E73" headerRowCount="1">
-  <autoFilter ref="A1:E73"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="AcceptanceCriteria" displayName="AcceptanceCriteria" ref="A1:E75" headerRowCount="1">
+  <autoFilter ref="A1:E75"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Criterion ID"/>
     <tableColumn id="2" name="Story"/>
@@ -303,8 +303,8 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="GapsandDecisions" displayName="GapsandDecisions" ref="A1:F15" headerRowCount="1">
-  <autoFilter ref="A1:F15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="GapsandDecisions" displayName="GapsandDecisions" ref="A1:F16" headerRowCount="1">
+  <autoFilter ref="A1:F16"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Gap ID"/>
     <tableColumn id="2" name="Question"/>
@@ -772,7 +772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1106,59 +1106,59 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>G11</t>
+          <t>G13</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Who may verify a phase by BAST.</t>
+          <t>How recognition becomes final when an Input or Output · unit job finishes under plan (cost &lt; budget or units &lt; planned) — % complete never reaches 100%, so the close gate could never pass.</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>PM or Finance; Finance alone may reverse (G6).</t>
+          <t>Once every work package is technically complete, Finance posts a completion true-up for the remaining contract value. The close gate checks recognised = contract value, not % complete = 100. Milestone projects finish by verifying every phase.</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Closed (assumed)</t>
+          <t>New requirement</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>REC-03</t>
+          <t>REC-04, REC-05, close (Story 16)</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Product + Finance</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>G12</t>
+          <t>G11</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Currency.</t>
+          <t>Who may verify a phase by BAST.</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>IDR only in MVP; multi-currency contracts out of scope.</t>
+          <t>PM or Finance; Finance alone may reverse (G6).</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Scope note</t>
+          <t>Closed (assumed)</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>REC-03</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -1170,49 +1170,49 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>OQ3</t>
+          <t>G12</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Accounting review of weights sourced from RAB.</t>
+          <t>Currency.</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Provisional: accept, editable by PM (plan Part 3).</t>
+          <t>IDR only in MVP; multi-currency contracts out of scope.</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Provisional</t>
+          <t>Scope note</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>PW-03</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Product</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>OQ6</t>
+          <t>OQ3</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Unit Output × service work package.</t>
+          <t>Accounting review of weights sourced from RAB.</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Provisional: option A.</t>
+          <t>Provisional: accept, editable by PM (plan Part 3).</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1222,42 +1222,74 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>REC-04</t>
+          <t>PW-03</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Product + Finance</t>
+          <t>Finance</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
+          <t>OQ6</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Unit Output × service work package.</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Provisional: option A.</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Provisional</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>REC-04</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Product + Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
           <t>OQ11</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Are billing terms specified in this PRD or the contract module?</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Provisional: the contract/SO module owns them; this module reads.</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Provisional</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>REC-08</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
@@ -1780,7 +1812,7 @@
         <is>
           <t>As a Finance/Controller, I want % complete = actual cost ÷ budget, recalculating live as cost posts, so that cost-to-cost jobs recognise revenue in step with the work actually done.
 PRD story: 8. Prototype: data/projectRecognition.ts percentComplete() input branch.
-Acceptance criteria: see sheet 'Acceptance Criteria' (REC-05-AC1…AC6).</t>
+Acceptance criteria: see sheet 'Acceptance Criteria' (REC-05-AC1…AC7).</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1832,7 +1864,7 @@
         <is>
           <t>As a Finance/Controller, I want every unbilled time entry to carry a bill, write-down or write-up decision before invoicing, so that what reaches the customer is a deliberate decision, not a raw timesheet dump.
 PRD story: 8. Prototype: tabs/RecognitionTab.vue T&amp;M table; projectActions.ts setTmDecision().
-Acceptance criteria: see sheet 'Acceptance Criteria' (REC-06-AC1…AC5).</t>
+Acceptance criteria: see sheet 'Acceptance Criteria' (REC-06-AC1…AC6).</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1982,7 +2014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3279,7 +3311,7 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Given Kamala seed (36 of 80 units, 30% recognised), Then % complete reads 45% and Recognition due Rp100.410.000.</t>
+          <t>Given Kamala seed (36 of 80 units; Rp194.940.000 recognised incl. the VO-2606-01 catch-up; contract Rp649.800.000), Then % complete reads 45% and Recognition due Rp97.470.000.</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -3534,22 +3566,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>REC-06-AC1</t>
+          <t>REC-05-AC7</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>REC-06</t>
+          <t>REC-05</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Happy path</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Given a T&amp;M project, Then unbilled entries list person, description, hours, cost, standard amount at bill rate and a Decision select that starts at “Decide…”.</t>
+          <t>Given every work package is technically complete but % complete &lt; 100% (finished under budget), Then Finance can post a completion true-up for the remaining contract value, and the close gate treats recognition as final once recognised = contract value (G13).</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -3561,7 +3593,7 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>REC-06-AC2</t>
+          <t>REC-06-AC1</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -3576,7 +3608,7 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Given Bill, Then bill amount = hours × bill rate.</t>
+          <t>Given a T&amp;M project, Then unbilled entries list person, description, hours, cost, standard amount at bill rate and a Decision select that starts at “Decide…”.</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -3588,7 +3620,7 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>REC-06-AC3</t>
+          <t>REC-06-AC2</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
@@ -3603,7 +3635,7 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Given Write-down or Write-up, Then a bill amount and a reason are required and the change is audited.</t>
+          <t>Given Bill, Then bill amount = hours × bill rate.</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -3615,7 +3647,7 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>REC-06-AC4</t>
+          <t>REC-06-AC3</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
@@ -3630,7 +3662,7 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Given entries still at “Decide…”, Then a counter shows how many are awaiting a decision.</t>
+          <t>Given Write-down or Write-up, Then a bill amount and a reason are required and the change is audited.</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -3642,7 +3674,7 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>REC-06-AC5</t>
+          <t>REC-06-AC4</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
@@ -3652,12 +3684,12 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Edge</t>
+          <t>Happy path</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Given an invoiced entry, Then its decision is read-only and shows the invoice number.</t>
+          <t>Given entries still at “Decide…”, Then a counter shows how many are awaiting a decision.</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -3669,22 +3701,22 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>REC-07-AC1</t>
+          <t>REC-06-AC5</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>REC-07</t>
+          <t>REC-06</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Happy path</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Given decided, uninvoiced entries, When I choose Invoice decided entries, Then one invoice is created for the sum of bill amounts.</t>
+          <t>Given an invoiced entry, Then its decision is read-only and shows the invoice number.</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -3696,22 +3728,22 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>REC-07-AC2</t>
+          <t>REC-06-AC6</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>REC-07</t>
+          <t>REC-06</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Rule</t>
+          <t>Data check</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Given the same action, Then one recognition posting of the same amount is created as a separate record.</t>
+          <t>Given PS-2604 entry TS/2026/0522 (7 h × Rp500.000 = Rp3.500.000), When I choose Write-down to Rp1.750.000 with a reason, Then the entry bills Rp1.750.000 and the audit entry reads “Write-down on TS/2026/0522: Rp3.500.000 → Rp1.750.000”.</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -3723,7 +3755,7 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>REC-07-AC3</t>
+          <t>REC-07-AC1</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
@@ -3733,12 +3765,12 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Edge</t>
+          <t>Happy path</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Given undecided entries, Then they are left out and the result states how many remain.</t>
+          <t>Given decided, uninvoiced entries, When I choose Invoice decided entries, Then one invoice is created for the sum of bill amounts.</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -3750,7 +3782,7 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>REC-07-AC4</t>
+          <t>REC-07-AC2</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -3760,12 +3792,12 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Rule</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Given no decided entries, Then the action is disabled with the reason.</t>
+          <t>Given the same action, Then one recognition posting of the same amount is created as a separate record.</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -3777,22 +3809,22 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>REC-08-AC1</t>
+          <t>REC-07-AC3</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>REC-08</t>
+          <t>REC-07</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Happy path</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Given a project linked to a contract/SO, Then its billing terms are listed with share, trigger, amount and invoice status — read from the contract module (OQ11).</t>
+          <t>Given undecided entries, Then they are left out and the result states how many remain.</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -3804,22 +3836,22 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>REC-08-AC2</t>
+          <t>REC-07-AC4</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>REC-08</t>
+          <t>REC-07</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Happy path</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Given a trigger (on signing / cumulative progress ≥ x% / at handover), Then its status shows Trigger met or Not met yet.</t>
+          <t>Given no decided entries, Then the action is disabled with the reason.</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -3831,7 +3863,7 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>REC-08-AC3</t>
+          <t>REC-08-AC1</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
@@ -3841,12 +3873,12 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Rule</t>
+          <t>Happy path</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Given Issue term invoice, Then one invoice is created for share × current contract value and no recognition posting is created.</t>
+          <t>Given a project linked to a contract/SO, Then its billing terms are listed with share, trigger, amount and invoice status — read from the contract module (OQ11).</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -3858,7 +3890,7 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>REC-08-AC4</t>
+          <t>REC-08-AC2</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -3868,12 +3900,12 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Edge</t>
+          <t>Happy path</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Given the trigger is not met, Then the confirm dialog warns but still allows issuing if the customer agreed.</t>
+          <t>Given a trigger (on signing / cumulative progress ≥ x% / at handover), Then its status shows Trigger met or Not met yet.</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -3885,7 +3917,7 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>REC-08-AC5</t>
+          <t>REC-08-AC3</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
@@ -3895,12 +3927,12 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Happy path</t>
+          <t>Rule</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Given the confirm dialog, Then it previews WIP after the invoice.</t>
+          <t>Given Issue term invoice, Then one invoice is created for share × current contract value and no recognition posting is created.</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -3912,7 +3944,7 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>REC-08-AC6</t>
+          <t>REC-08-AC4</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -3922,12 +3954,12 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Data check</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Given a DP invoice before any progress, Then WIP shows an overbilled liability equal to the DP.</t>
+          <t>Given the trigger is not met, Then the confirm dialog warns but still allows issuing if the customer agreed.</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -3939,25 +3971,79 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
+          <t>REC-08-AC5</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>REC-08</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>Happy path</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Given the confirm dialog, Then it previews WIP after the invoice.</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>REC-08-AC6</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>REC-08</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>Data check</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>Given a DP invoice before any progress, Then WIP shows an overbilled liability equal to the DP.</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>Not written</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
           <t>REC-08-AC7</t>
         </is>
       </c>
-      <c r="B73" s="5" t="inlineStr">
+      <c r="B75" s="5" t="inlineStr">
         <is>
           <t>REC-08</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C75" s="5" t="inlineStr">
         <is>
           <t>Rule</t>
         </is>
       </c>
-      <c r="D73" s="5" t="inlineStr">
+      <c r="D75" s="5" t="inlineStr">
         <is>
           <t>Given terms that don’t align with phases (IPB: DP 30% / progress 50% / settlement 20% vs 5 phases), Then nothing tries to map terms to phases.</t>
         </is>
       </c>
-      <c r="E73" s="5" t="inlineStr">
+      <c r="E75" s="5" t="inlineStr">
         <is>
           <t>Not written</t>
         </is>
